--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N28_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0001T0006Z000C1N28_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.22009459937911</v>
+        <v>6.698265372399105</v>
       </c>
       <c r="D2" t="n">
-        <v>23.99204808088653</v>
+        <v>3.89870781314406</v>
       </c>
       <c r="E2" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F2" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.82357028760858</v>
+        <v>7.283830171736395</v>
       </c>
       <c r="D3" t="n">
-        <v>30.92364926090752</v>
+        <v>5.025093004897473</v>
       </c>
       <c r="E3" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F3" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.58011828085672</v>
+        <v>6.269269220639218</v>
       </c>
       <c r="D4" t="n">
-        <v>24.01359097738488</v>
+        <v>3.902208533825043</v>
       </c>
       <c r="E4" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F4" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>36.96196172923312</v>
+        <v>6.006318781000382</v>
       </c>
       <c r="D5" t="n">
-        <v>26.36680218951903</v>
+        <v>4.284605355796843</v>
       </c>
       <c r="E5" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F5" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.870756031793504</v>
+        <v>0.7914978551664444</v>
       </c>
       <c r="D6" t="n">
-        <v>18.81891564546642</v>
+        <v>3.058073792388294</v>
       </c>
       <c r="E6" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F6" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.906965146258827</v>
+        <v>1.609881836267059</v>
       </c>
       <c r="D7" t="n">
-        <v>15.83663648299705</v>
+        <v>2.573453428487021</v>
       </c>
       <c r="E7" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F7" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>14.54167268388427</v>
+        <v>2.363021811131194</v>
       </c>
       <c r="D8" t="n">
-        <v>13.86245838795539</v>
+        <v>2.25264948804275</v>
       </c>
       <c r="E8" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F8" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.55774121841423</v>
+        <v>2.040632947992312</v>
       </c>
       <c r="D9" t="n">
-        <v>9.546040504854201</v>
+        <v>1.551231582038808</v>
       </c>
       <c r="E9" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F9" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.48881911847927</v>
+        <v>2.841933106752882</v>
       </c>
       <c r="D10" t="n">
-        <v>5.323321650177768</v>
+        <v>0.8650397681538874</v>
       </c>
       <c r="E10" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F10" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>15.39215325528122</v>
+        <v>2.501224903983199</v>
       </c>
       <c r="D11" t="n">
-        <v>16.5889103179793</v>
+        <v>2.695697926671637</v>
       </c>
       <c r="E11" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F11" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.23387231870829</v>
+        <v>5.888004251790097</v>
       </c>
       <c r="D12" t="n">
-        <v>23.796383354963</v>
+        <v>3.866912295181487</v>
       </c>
       <c r="E12" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F12" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.14854401280227</v>
+        <v>3.436638402080369</v>
       </c>
       <c r="D13" t="n">
-        <v>3.440128600070947</v>
+        <v>0.5590208975115289</v>
       </c>
       <c r="E13" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F13" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>32.03207442852934</v>
+        <v>5.205212094636019</v>
       </c>
       <c r="D14" t="n">
-        <v>4.47213595499958</v>
+        <v>0.7267220926874317</v>
       </c>
       <c r="E14" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F14" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.18521423879344</v>
+        <v>6.530097313803934</v>
       </c>
       <c r="D15" t="n">
-        <v>40.02068348534822</v>
+        <v>6.503361066369086</v>
       </c>
       <c r="E15" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F15" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>19.23415679004562</v>
+        <v>3.125550478382413</v>
       </c>
       <c r="D16" t="n">
-        <v>18.32534232183747</v>
+        <v>2.97786812729859</v>
       </c>
       <c r="E16" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F16" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>28.24767394559391</v>
+        <v>4.59024701615901</v>
       </c>
       <c r="D17" t="n">
-        <v>12.73567314493791</v>
+        <v>2.06954688605241</v>
       </c>
       <c r="E17" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F17" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.00396868861773</v>
+        <v>6.825644911900381</v>
       </c>
       <c r="D18" t="n">
-        <v>7.158910531638177</v>
+        <v>1.163322961391204</v>
       </c>
       <c r="E18" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F18" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>18.84927415432518</v>
+        <v>3.063007050077843</v>
       </c>
       <c r="D19" t="n">
-        <v>18.68533609552962</v>
+        <v>3.036367115523563</v>
       </c>
       <c r="E19" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F19" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>29.31861802504388</v>
+        <v>4.764275429069631</v>
       </c>
       <c r="D20" t="n">
-        <v>13.72745668483335</v>
+        <v>2.230711711285419</v>
       </c>
       <c r="E20" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F20" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>40.98065836287338</v>
+        <v>6.659356983966924</v>
       </c>
       <c r="D21" t="n">
-        <v>2.570806292860011</v>
+        <v>0.4177560225897519</v>
       </c>
       <c r="E21" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F21" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>16.46936602117299</v>
+        <v>2.676271978440611</v>
       </c>
       <c r="D22" t="n">
-        <v>15.91262612756148</v>
+        <v>2.585801745728741</v>
       </c>
       <c r="E22" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F22" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>35.54990340008283</v>
+        <v>5.77685930251346</v>
       </c>
       <c r="D23" t="n">
-        <v>7.26421534714752</v>
+        <v>1.180434993911472</v>
       </c>
       <c r="E23" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F23" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>48.59362389553056</v>
+        <v>7.896463883023715</v>
       </c>
       <c r="D24" t="n">
-        <v>7.032673847631306</v>
+        <v>1.142809500240087</v>
       </c>
       <c r="E24" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F24" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>53.02469334874846</v>
+        <v>8.616512669171625</v>
       </c>
       <c r="D25" t="n">
-        <v>9.594977355364319</v>
+        <v>1.559183820246702</v>
       </c>
       <c r="E25" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F25" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>33.59258916130756</v>
+        <v>5.458795738712478</v>
       </c>
       <c r="D26" t="n">
-        <v>19.19849033778437</v>
+        <v>3.119754679889961</v>
       </c>
       <c r="E26" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F26" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>17.97686142419618</v>
+        <v>2.921239981431879</v>
       </c>
       <c r="D27" t="n">
-        <v>18.61422092167829</v>
+        <v>3.024810899772722</v>
       </c>
       <c r="E27" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F27" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>43.80858630554354</v>
+        <v>7.118895274650826</v>
       </c>
       <c r="D28" t="n">
-        <v>9.301042226299185</v>
+        <v>1.511419361773618</v>
       </c>
       <c r="E28" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F28" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>40.22793680483241</v>
+        <v>6.537039730785267</v>
       </c>
       <c r="D29" t="n">
-        <v>40.97070315434133</v>
+        <v>6.657739262580466</v>
       </c>
       <c r="E29" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F29" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>25.51338095655241</v>
+        <v>4.145924405439767</v>
       </c>
       <c r="D30" t="n">
-        <v>20.67818353060386</v>
+        <v>3.360204823723127</v>
       </c>
       <c r="E30" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F30" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>38.81234611034037</v>
+        <v>6.307006242930311</v>
       </c>
       <c r="D31" t="n">
-        <v>39.00102428364871</v>
+        <v>6.337666446092916</v>
       </c>
       <c r="E31" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F31" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>9.508217940941339</v>
+        <v>1.545085415402968</v>
       </c>
       <c r="D32" t="n">
-        <v>9.163639843628603</v>
+        <v>1.489091474589648</v>
       </c>
       <c r="E32" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F32" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>33.737812840218</v>
+        <v>5.482394586535425</v>
       </c>
       <c r="D33" t="n">
-        <v>33.50660439329842</v>
+        <v>5.444823213910994</v>
       </c>
       <c r="E33" t="n">
-        <v>12.76335356686646</v>
+        <v>2.0740449546158</v>
       </c>
       <c r="F33" t="n">
-        <v>10.54191579247363</v>
+        <v>1.713061316276965</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
